--- a/artfynd/A 55734-2025 artfynd.xlsx
+++ b/artfynd/A 55734-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131917957</v>
       </c>
       <c r="B2" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 55734-2025 artfynd.xlsx
+++ b/artfynd/A 55734-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131917957</v>
       </c>
       <c r="B2" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 55734-2025 artfynd.xlsx
+++ b/artfynd/A 55734-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131917957</v>
       </c>
       <c r="B2" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 55734-2025 artfynd.xlsx
+++ b/artfynd/A 55734-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131917957</v>
+        <v>119262636</v>
       </c>
       <c r="B2" t="n">
-        <v>79327</v>
+        <v>93189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>4361</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sinksundberget, Sinksundberget, Nb</t>
+          <t>Ormberget, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>831064</v>
+        <v>831216</v>
       </c>
       <c r="R2" t="n">
-        <v>7295641</v>
+        <v>7295750</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,22 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>17:39</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>17:39</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,21 +757,245 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Tallskog på blockmark</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>131917957</v>
+      </c>
+      <c r="B3" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Sinksundberget, Sinksundberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>831064</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7295641</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Luleå</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Nederluleå</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Christina Boyd</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Christina Boyd</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>114090199</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100806</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222584</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Bergsslok</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Melica nutans</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hertsöberget, 350 m NO-NNO om triangelpkt 76,2, Nb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>831148</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7295678</v>
+      </c>
+      <c r="S4" t="n">
+        <v>100</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Luleå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Nederluleå</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>1998-07-26</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>1998-07-26</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Norrbottens flora - 2010.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>igenväxande äng</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Mora Aronsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Lennart Stenberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Norrbottens flora 2010</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
